--- a/new-stats/sk-artis-brno.xlsx
+++ b/new-stats/sk-artis-brno.xlsx
@@ -685,22 +685,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ostrava</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Artis Brno</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
